--- a/Assets/06.Data/Origin/HeroData.xlsx
+++ b/Assets/06.Data/Origin/HeroData.xlsx
@@ -576,7 +576,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>44</v>
@@ -605,7 +605,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>45</v>
@@ -634,7 +634,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>46</v>
@@ -663,7 +663,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>47</v>
@@ -692,7 +692,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>48</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>49</v>
@@ -750,7 +750,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>50</v>
@@ -779,7 +779,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>51</v>
@@ -808,7 +808,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>52</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>53</v>
